--- a/Thesis/Lastenheft Bachelorarbeit.xlsx
+++ b/Thesis/Lastenheft Bachelorarbeit.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10523"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7941FFE3-5EBD-A54F-A201-2657AD03C867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A546050-F591-7B43-8A18-935EF1FED291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="108">
   <si>
     <t>Requirements Specification ("Lastenheft")</t>
   </si>
@@ -282,15 +282,9 @@
     <t>Kommentare + Unterfunktionen</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wie bei matter Webseite anlegen </t>
   </si>
   <si>
-    <t>Open Source Broker (iO Broker Open hab)</t>
-  </si>
-  <si>
     <t>Weiterverwendung der Daten</t>
   </si>
   <si>
@@ -333,9 +327,6 @@
     <t>I2C + Protokoll dargestellt (Kap3_2+3_3+4_3)</t>
   </si>
   <si>
-    <t>Operatinal +; documented ~</t>
-  </si>
-  <si>
     <t xml:space="preserve">Esp_matter.h /.cpp Dateien </t>
   </si>
   <si>
@@ -355,6 +346,12 @@
   </si>
   <si>
     <t>Beispielnutzung (Büro)</t>
+  </si>
+  <si>
+    <t>Matter Bindung aber nur wifi</t>
+  </si>
+  <si>
+    <t>Operatinal +; documented +</t>
   </si>
 </sst>
 </file>
@@ -640,7 +637,7 @@
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>81</v>
       </c>
       <c r="E11" s="8" t="b">
@@ -690,7 +687,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E14" s="8" t="b">
         <v>1</v>
@@ -707,7 +704,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E15" s="8" t="b">
         <v>1</v>
@@ -724,7 +721,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E16" s="8" t="b">
         <v>1</v>
@@ -744,7 +741,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E18" s="8" t="b">
         <v>0</v>
@@ -761,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E19" s="8" t="b">
         <v>0</v>
@@ -778,7 +775,7 @@
         <v>29</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E20" s="8" t="b">
         <v>1</v>
@@ -795,7 +792,7 @@
         <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E21" s="8" t="b">
         <v>1</v>
@@ -812,7 +809,7 @@
         <v>33</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E23" s="8" t="b">
         <v>1</v>
@@ -829,7 +826,7 @@
         <v>35</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E24" s="8" t="b">
         <v>1</v>
@@ -864,10 +861,10 @@
         <v>39</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E27" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
@@ -881,7 +878,7 @@
         <v>41</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E28" s="8" t="b">
         <v>1</v>
@@ -898,10 +895,10 @@
         <v>43</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E29" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
@@ -915,7 +912,7 @@
         <v>45</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E30" s="8" t="b">
         <v>1</v>
@@ -932,7 +929,7 @@
         <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E31" s="8" t="b">
         <v>1</v>
@@ -952,13 +949,13 @@
         <v>50</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E33" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -972,7 +969,7 @@
         <v>52</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E34" s="8" t="b">
         <v>0</v>
@@ -1004,7 +1001,7 @@
         <v>56</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E36" s="8" t="b">
         <v>0</v>
@@ -1021,7 +1018,7 @@
         <v>58</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E37" s="8" t="b">
         <v>1</v>
@@ -1041,10 +1038,10 @@
         <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E39" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
@@ -1058,7 +1055,7 @@
         <v>62</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E40" s="8" t="b">
         <v>1</v>
@@ -1075,10 +1072,10 @@
         <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="E41" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
@@ -1106,10 +1103,10 @@
         <v>68</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E43" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
@@ -1123,7 +1120,7 @@
         <v>70</v>
       </c>
       <c r="D44" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E44" s="8" t="b">
         <v>0</v>
@@ -1168,7 +1165,7 @@
         <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E48" s="8" t="b">
         <v>0</v>
@@ -1185,10 +1182,10 @@
         <v>77</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E49" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
